--- a/04_DESIGN_TABLES/DesignTable_1602.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1602.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -852,24 +857,71 @@
           <t>1602-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.405</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>1602-02-02-02-FG</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1/8-27 (A NPTF) x 1/8-27 (A1 (2) NPSM) x 1/8-27 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1602-02-02-02-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 bd13e0f1d734ade1...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -880,6 +932,11 @@
       <c r="V7" t="inlineStr">
         <is>
           <t>1602-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -889,24 +946,71 @@
           <t>1602-04-04-04-FG</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.54</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>1602-04-04-04-FG</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF) x 1/4-18 (A1 (2) NPSM) x 1/4-18 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1602-04-04-04-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 6a09e2913f5719a4...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -917,6 +1021,11 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>1602-04-04-04-FG</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -926,24 +1035,71 @@
           <t>1602-06-06-06-FG</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.675</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>1602-06-06-06-FG</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3/8-18 (A NPTF) x 3/8-18 (A1 (2) NPSM) x 3/8-18 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1602-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1602-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1602-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1602-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -954,6 +1110,11 @@
       <c r="V9" t="inlineStr">
         <is>
           <t>1602-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -963,24 +1124,71 @@
           <t>1602-08-08-08-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.84</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>1602-08-08-08-FG</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF) x 1/2-14 (A1 (2) NPSM) x 1/2-14 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1602-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1602-08-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1602-08-08-08-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 4007561bbf56f766...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1602-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1602-08-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -991,6 +1199,11 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>1602-08-08-08-FG</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1000,24 +1213,71 @@
           <t>1602-12-12-12-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.05</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>1602-12-12-12-FG</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-14 (A1 (2) NPSM) x 3/4-14 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1602-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1602-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1602-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1602-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1028,6 +1288,11 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>1602-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1037,24 +1302,71 @@
           <t>1602-16-16-16-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.315</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>1602-16-16-16-FG</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF) x 1-11 1/2 (A1 (2) NPSM) x 1-11 1/2 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1602-16-16-16-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 3513b64f1275259b...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1065,6 +1377,11 @@
       <c r="V12" t="inlineStr">
         <is>
           <t>1602-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1391,71 @@
           <t>1602-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.66</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>1602-20-20-20-FG</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF) x 1 1/4-11 1/2 (A1 (2) NPSM) x 1 1/4-11 1/2 (A1 (3) NPSM)</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1602-20-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 4f1a70c50dfae6ab...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08)</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1102,6 +1466,11 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>1602-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>OMI-DRAWING</t>
         </is>
       </c>
     </row>
